--- a/src/test/resources/ImportFile/Collection1.xlsx
+++ b/src/test/resources/ImportFile/Collection1.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23127"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever\src\test\resources\ImportFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F5171A-B3DB-45A7-BAD2-7A2E1EBA3D47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5028F1-29AC-4D9D-9A0D-61F91B9ADD62}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>S.No</t>
   </si>
@@ -31,6 +36,9 @@
     <t>Collections</t>
   </si>
   <si>
+    <t>Brand Type</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -53,6 +61,12 @@
   </si>
   <si>
     <t>Sale</t>
+  </si>
+  <si>
+    <t>Urban Laado-1</t>
+  </si>
+  <si>
+    <t>Zlaata India</t>
   </si>
   <si>
     <t>ZL001
@@ -68,10 +82,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Auto456</t>
-  </si>
-  <si>
-    <t>Auto-456</t>
+    <t>Automation2</t>
   </si>
 </sst>
 </file>
@@ -149,7 +160,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -165,7 +176,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -177,7 +188,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -191,12 +202,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -224,14 +235,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -259,6 +287,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -401,15 +446,20 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="7.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -440,51 +490,57 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="244.8">
+    <row r="2" spans="1:12" ht="244.8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="K2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
+      <c r="L2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="I2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>